--- a/Issue Tracker.xlsx
+++ b/Issue Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://boeing-my.sharepoint.us/personal/fred_l_templin_boeing_com/Documents/Documents/src/ietf/draft-ietf-manet-inet-gap-analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="316" documentId="11_F25DC773A252ABDACC1048E5219F4F4A5BDE58F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD73E1EE-0679-4EC7-B460-4B1091C76014}"/>
+  <xr:revisionPtr revIDLastSave="360" documentId="11_F25DC773A252ABDACC1048E5219F4F4A5BDE58F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EB62081-BC05-4B68-A076-9036FD8EBAD6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="77">
   <si>
     <t>Issue number:</t>
   </si>
@@ -355,17 +355,6 @@
 and not as it's own problem statement.</t>
   </si>
   <si>
-    <t>Lou Berger 7/22/2026 MANET list post
-Draft Version: -04
-Discuss for: -05</t>
-  </si>
-  <si>
-    <t>Lou Berger 7/22/2026 MANET list post
-Draft Version: -03
-Resolved in: -04
-Discuss for: -05</t>
-  </si>
-  <si>
     <t>The document includes text on what is meant by "problem" and what is meant by "gap", and other problem statement and gap analysis RFCs have gone forward in their own ways. Proposed resolution: include definitions for "problem" and "gap" in the terminology section.</t>
   </si>
   <si>
@@ -400,15 +389,38 @@
     <t>The resolution to issue #21 includes new text about the expectations of the DNS for reverse-DNS lookups in the overlay routing system. DNS usage expectation are also cited elsewhere throughout the -04 . This seems sufficient for a problem statement document, but if a separate section on DNS is needed it can be added to -05.</t>
   </si>
   <si>
-    <t>August 1, 2026
+    <t>August 5, 2026
 Draft Version: -04
 Resolved in: -05</t>
   </si>
   <si>
-    <t>Added citations plus appropriate supporting text</t>
-  </si>
-  <si>
-    <t>Editorial action: Draft needs to cite Multilink Subnet (RFC4903) and Unique IPv6 Prefix Per Client (RFC9663).</t>
+    <t>Lou Berger 7/22/2026 MANET list post
+Draft Version: -04
+Discuss for: future version</t>
+  </si>
+  <si>
+    <t>Lou Berger 7/22/2026 MANET list post
+Draft Version: -03
+Resolved in: -04
+Discuss for: future version</t>
+  </si>
+  <si>
+    <t>Editorial action: Problem #1 needs to discuss partitions and merges and their implications. Draft needs to cite Multilink Subnet (RFC4903) and Unique IPv6 Prefix Per Client (RFC9663).</t>
+  </si>
+  <si>
+    <t>Added problem, citations plus appropriate supporting text</t>
+  </si>
+  <si>
+    <t>Christoper Dearlove; Henning Rogge comments at IETF126.
+July 22, 2026
+Draft Version: -04
+Resolved in: -05</t>
+  </si>
+  <si>
+    <t>Draft should cite OSPF-MDR, OLSRv2, Babel. Clarify justification for cellphones as MANET routers.</t>
+  </si>
+  <si>
+    <t>Added routing protocol citations. Added cellphone as MANET router justification.</t>
   </si>
 </sst>
 </file>
@@ -516,6 +528,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -781,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -885,7 +901,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
@@ -893,13 +909,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="360" x14ac:dyDescent="0.3">
@@ -1103,13 +1119,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>60</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
@@ -1131,13 +1147,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
@@ -1145,31 +1161,42 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>59</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A27">
+        <v>27</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" s="4" t="s">
+      <c r="B28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" t="s">
         <v>73</v>
       </c>
-      <c r="D27" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C29" s="2"/>
@@ -1186,11 +1213,8 @@
     <row r="33" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C33" s="2"/>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C34" s="2"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="nOwZW4UqyMLUVz2dCtlkTpEU3otWfXTZit7Hwm/RSLevR2f7iXsqwZA8zQQ4pQ7An9MRd0tvJCFtmodd0xatUw==" saltValue="aekYvS3GqPmTD5H+hV9Eug==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ocBfZSSGyGehk6veryE32jAbV89wT9+SUaaCtbvAG4g7VAQFj1oXV7//Z/6kX72f+gFojbbfCYBJRanEatVJEQ==" saltValue="QBZxAG2tjZiakfvYWecbLA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Issue Tracker.xlsx
+++ b/Issue Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://boeing-my.sharepoint.us/personal/fred_l_templin_boeing_com/Documents/Documents/src/ietf/draft-ietf-manet-inet-gap-analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="360" documentId="11_F25DC773A252ABDACC1048E5219F4F4A5BDE58F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EB62081-BC05-4B68-A076-9036FD8EBAD6}"/>
+  <xr:revisionPtr revIDLastSave="363" documentId="11_F25DC773A252ABDACC1048E5219F4F4A5BDE58F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C714BF15-0740-478D-AEE9-07E9D0AA4995}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -386,9 +386,6 @@
     <t xml:space="preserve">This service that is termed "multilink" is not currently discussed in the draft and I do not think it needs to be added to the draft. With an overlay, the IP address seen by the application layer is covered by a prefix in the overlay routing system while the IP addresses seen by the link layer are covered by prefixes in the standard Internet routing system. Without an overlay, there is no overlay routing system and all IP addresses need  to be covered by prefixes in the Internet routing system. This difference involves many architectural consideration that would require a deeper discussion. Mulitlink is just one aspect among many aspects that occur when an overlay is involved, and it seems beyond the scope of this document to try to exhaustively cover all arhchitectural implications of including an overlay.   </t>
   </si>
   <si>
-    <t>The resolution to issue #21 includes new text about the expectations of the DNS for reverse-DNS lookups in the overlay routing system. DNS usage expectation are also cited elsewhere throughout the -04 . This seems sufficient for a problem statement document, but if a separate section on DNS is needed it can be added to -05.</t>
-  </si>
-  <si>
     <t>August 5, 2026
 Draft Version: -04
 Resolved in: -05</t>
@@ -421,6 +418,9 @@
   </si>
   <si>
     <t>Added routing protocol citations. Added cellphone as MANET router justification.</t>
+  </si>
+  <si>
+    <t>The resolution to issue #21 includes new text about the expectations of the DNS for reverse-DNS lookups in the overlay routing system. DNS usage expectation are also cited elsewhere throughout the -04 . This seems sufficient for a problem statement document, but if a separate section on DNS is needed it can be added to a later draft version.</t>
   </si>
 </sst>
 </file>
@@ -528,10 +528,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1119,7 +1115,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>60</v>
@@ -1161,13 +1157,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>59</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="72" x14ac:dyDescent="0.3">
@@ -1175,13 +1171,13 @@
         <v>27</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -1189,13 +1185,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C28" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" t="s">
         <v>72</v>
-      </c>
-      <c r="D28" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -1214,7 +1210,7 @@
       <c r="C33" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ocBfZSSGyGehk6veryE32jAbV89wT9+SUaaCtbvAG4g7VAQFj1oXV7//Z/6kX72f+gFojbbfCYBJRanEatVJEQ==" saltValue="QBZxAG2tjZiakfvYWecbLA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="uFx03kOnKCT1lQ+YsFvLxDIvczgJjfpx73vfBbK9FUgkfQcsSzvbBj2pcaEj06y+isD2Vy9T8ZUVsZpxD+cY8g==" saltValue="T9fpiIEdfkI4nLzQpRXB3Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Issue Tracker.xlsx
+++ b/Issue Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://boeing-my.sharepoint.us/personal/fred_l_templin_boeing_com/Documents/Documents/src/ietf/draft-ietf-manet-inet-gap-analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="363" documentId="11_F25DC773A252ABDACC1048E5219F4F4A5BDE58F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C714BF15-0740-478D-AEE9-07E9D0AA4995}"/>
+  <xr:revisionPtr revIDLastSave="373" documentId="11_F25DC773A252ABDACC1048E5219F4F4A5BDE58F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C2B53F8-95A3-47D5-A8B1-4389D14B0424}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="80">
   <si>
     <t>Issue number:</t>
   </si>
@@ -421,6 +421,17 @@
   </si>
   <si>
     <t>The resolution to issue #21 includes new text about the expectations of the DNS for reverse-DNS lookups in the overlay routing system. DNS usage expectation are also cited elsewhere throughout the -04 . This seems sufficient for a problem statement document, but if a separate section on DNS is needed it can be added to a later draft version.</t>
+  </si>
+  <si>
+    <t>August 12, 2026
+Draft Version: -05
+Resolved in: -06</t>
+  </si>
+  <si>
+    <t>Editorial action: Problem #1 needs to discuss mobility. Also, a singleton isolated MANET router is considered a MANET unto itself. Clarifications on the expectation of cellphones to serve as MANET routers.</t>
+  </si>
+  <si>
+    <t>Made editorial updates.</t>
   </si>
 </sst>
 </file>
@@ -528,6 +539,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1194,8 +1209,19 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C29" s="2"/>
+    <row r="29" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C30" s="2"/>
@@ -1210,7 +1236,7 @@
       <c r="C33" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="uFx03kOnKCT1lQ+YsFvLxDIvczgJjfpx73vfBbK9FUgkfQcsSzvbBj2pcaEj06y+isD2Vy9T8ZUVsZpxD+cY8g==" saltValue="T9fpiIEdfkI4nLzQpRXB3Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="xoa9nSINmt8UqRmKhwsdihORsLQ97VN5PuNLMdRioeYpsxQIPwFvA0zWFfFjzaQm9A4OHEeah8+L5QmMb0Yr7g==" saltValue="ZSZ1LHC7rwv0/UOxyfiv/A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
